--- a/artfynd/A 53138-2022 artfynd.xlsx
+++ b/artfynd/A 53138-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53138-2022 artfynd.xlsx
+++ b/artfynd/A 53138-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89088706</v>
+        <v>97203424</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grottan, Påryd, Sm</t>
+          <t>Runtorp 3:5, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558056.0206839687</v>
+        <v>557998</v>
       </c>
       <c r="R2" t="n">
-        <v>6273171.555692272</v>
+        <v>6273283</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96064018</v>
+        <v>97203429</v>
       </c>
       <c r="B3" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,45 +787,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korsning Bockamossen Ö, Sm</t>
+          <t>Runtorp 3:5, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558050.5887899271</v>
+        <v>558008</v>
       </c>
       <c r="R3" t="n">
-        <v>6273165.425222244</v>
+        <v>6273278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96064089</v>
+        <v>97203430</v>
       </c>
       <c r="B4" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,45 +889,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bockamossen 300m Ö, Sm</t>
+          <t>Runtorp 3:5, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557868.5678550903</v>
+        <v>558008</v>
       </c>
       <c r="R4" t="n">
-        <v>6273204.209537803</v>
+        <v>6273278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,61 +980,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96064100</v>
+        <v>112888542</v>
       </c>
       <c r="B5" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bockamossen 300m Ö, Sm</t>
+          <t>Korsning Bockamossen Ö, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557820.5095137022</v>
+        <v>558042</v>
       </c>
       <c r="R5" t="n">
-        <v>6273209.054814801</v>
+        <v>6273134</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1060,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1171,57 +1078,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96064086</v>
+        <v>89088706</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bockamossen 300m Ö, Sm</t>
+          <t>Grottan, Påryd, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557869.1193816101</v>
+        <v>558056</v>
       </c>
       <c r="R6" t="n">
-        <v>6273204.217112752</v>
+        <v>6273172</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,22 +1154,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,15 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96064071</v>
+        <v>96064018</v>
       </c>
       <c r="B7" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,14 +1229,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bockamossen 300m Ö, Sm</t>
+          <t>Korsning Bockamossen Ö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557867.1624293054</v>
+        <v>558051</v>
       </c>
       <c r="R7" t="n">
-        <v>6273226.210427837</v>
+        <v>6273166</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,19 +1266,9 @@
           <t>2021-09-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,12 +1299,7 @@
         <v>96064046</v>
       </c>
       <c r="B8" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557871.612761777</v>
+        <v>557871</v>
       </c>
       <c r="R8" t="n">
-        <v>6273183.332069556</v>
+        <v>6273184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,19 +1375,9 @@
           <t>2021-09-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,62 +1405,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97203409</v>
+        <v>96064071</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Runtorp 3:5, Sm</t>
+          <t>Bockamossen 300m Ö, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558006.0402840954</v>
+        <v>557867</v>
       </c>
       <c r="R9" t="n">
-        <v>6273235.827141202</v>
+        <v>6273227</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,22 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,62 +1514,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97203435</v>
+        <v>96064089</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Runtorp 3:5, Sm</t>
+          <t>Bockamossen 300m Ö, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558049.5650600905</v>
+        <v>557868</v>
       </c>
       <c r="R10" t="n">
-        <v>6273239.729597154</v>
+        <v>6273204</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1743,22 +1590,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,62 +1623,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97203481</v>
+        <v>96064100</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Runtorp 3:5, Sm</t>
+          <t>Bockamossen 300m Ö, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558119.6007588374</v>
+        <v>557820</v>
       </c>
       <c r="R11" t="n">
-        <v>6273241.245603707</v>
+        <v>6273209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1868,22 +1699,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,62 +1732,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97203468</v>
+        <v>112888482</v>
       </c>
       <c r="B12" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Runtorp 3:5, Sm</t>
+          <t>Korsning Bockamossen Ö, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558135.1544193224</v>
+        <v>558035</v>
       </c>
       <c r="R12" t="n">
-        <v>6273273.389211363</v>
+        <v>6273146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,22 +1798,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2035,62 +1830,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97203470</v>
+        <v>112888513</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Runtorp 3:5, Sm</t>
+          <t>Korsning Bockamossen Ö, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558160.2189395622</v>
+        <v>558042</v>
       </c>
       <c r="R13" t="n">
-        <v>6273215.932391884</v>
+        <v>6273134</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2117,22 +1896,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2141,7 +1910,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2160,62 +1928,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97203359</v>
+        <v>112888622</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Runtorp 3:5, Sm</t>
+          <t>Korsning Bockamossen Ö, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557988.9127857743</v>
+        <v>558097</v>
       </c>
       <c r="R14" t="n">
-        <v>6273237.793388142</v>
+        <v>6273142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2242,22 +1994,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,7 +2008,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2285,62 +2026,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97203473</v>
+        <v>112888681</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Runtorp 3:5, Sm</t>
+          <t>Korsning Bockamossen Ö, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558123.4717535239</v>
+        <v>558096</v>
       </c>
       <c r="R15" t="n">
-        <v>6273200.561618768</v>
+        <v>6273158</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2367,22 +2092,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2391,7 +2106,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2410,62 +2124,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97203455</v>
+        <v>113730308</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Runtorp 3:5, Sm</t>
+          <t>Korsning Bockamossen Ö, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558104.3377416183</v>
+        <v>558096</v>
       </c>
       <c r="R16" t="n">
-        <v>6273268.009626345</v>
+        <v>6273158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2492,22 +2194,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2516,7 +2208,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2535,51 +2226,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97203328</v>
+        <v>97203468</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2587,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557980.2399116966</v>
+        <v>558135</v>
       </c>
       <c r="R17" t="n">
-        <v>6273226.663968845</v>
+        <v>6273274</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,28 +2306,17 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2660,15 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97203469</v>
+        <v>96064086</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2693,29 +2363,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Runtorp 3:5, Sm</t>
+          <t>Bockamossen 300m Ö, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558147.4093431056</v>
+        <v>557869</v>
       </c>
       <c r="R18" t="n">
-        <v>6273264.750338782</v>
+        <v>6273204</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2742,22 +2404,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,15 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97203438</v>
+        <v>97203328</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2467,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2837,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558050.4785220224</v>
+        <v>557980</v>
       </c>
       <c r="R19" t="n">
-        <v>6273253.504720736</v>
+        <v>6273227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2870,19 +2517,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2913,12 +2550,7 @@
         <v>97203333</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2962,10 +2594,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557980.0429858085</v>
+        <v>557980</v>
       </c>
       <c r="R20" t="n">
-        <v>6273240.974333957</v>
+        <v>6273241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2995,19 +2627,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3035,15 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97203462</v>
+        <v>97203359</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,7 +2687,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3087,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558125.3334039636</v>
+        <v>557989</v>
       </c>
       <c r="R21" t="n">
-        <v>6273265.546727523</v>
+        <v>6273238</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3120,19 +2737,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3160,15 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97203445</v>
+        <v>97203409</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3195,7 +2797,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3212,10 +2814,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558071.6312643129</v>
+        <v>558006</v>
       </c>
       <c r="R22" t="n">
-        <v>6273279.669666439</v>
+        <v>6273236</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,19 +2847,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3285,15 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97203480</v>
+        <v>97203435</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3337,10 +2924,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558135.0661538945</v>
+        <v>558050</v>
       </c>
       <c r="R23" t="n">
-        <v>6273239.807456805</v>
+        <v>6273240</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3370,19 +2957,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3410,15 +2987,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97203451</v>
+        <v>97203438</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3445,7 +3017,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3462,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558092.755856071</v>
+        <v>558051</v>
       </c>
       <c r="R24" t="n">
-        <v>6273267.849919928</v>
+        <v>6273254</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3495,19 +3067,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3538,12 +3100,7 @@
         <v>97203441</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3587,10 +3144,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558070.391684299</v>
+        <v>558070</v>
       </c>
       <c r="R25" t="n">
-        <v>6273289.561521648</v>
+        <v>6273290</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3620,19 +3177,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3660,15 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>100195381</v>
+        <v>97203445</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3695,7 +3237,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3708,14 +3250,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Runtorp, Sm</t>
+          <t>Runtorp 3:5, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557862.7882936193</v>
+        <v>558071</v>
       </c>
       <c r="R26" t="n">
-        <v>6273183.210874081</v>
+        <v>6273280</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3742,22 +3284,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3785,15 +3317,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>100195261</v>
+        <v>97203451</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3820,7 +3347,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3833,14 +3360,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Runtorp, Sm</t>
+          <t>Runtorp 3:5, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557899.9071508651</v>
+        <v>558092</v>
       </c>
       <c r="R27" t="n">
-        <v>6273171.609573652</v>
+        <v>6273268</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3867,22 +3394,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3910,15 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>100195736</v>
+        <v>97203455</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3945,7 +3457,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3953,23 +3465,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Runtorp, Sm</t>
+          <t>Runtorp 3:5, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557831.4191563765</v>
+        <v>558105</v>
       </c>
       <c r="R28" t="n">
-        <v>6273218.012620509</v>
+        <v>6273268</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3996,22 +3504,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4039,51 +3537,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112888681</v>
+        <v>97203462</v>
       </c>
       <c r="B29" t="n">
-        <v>90560</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Korsning Bockamossen Ö, Sm</t>
+          <t>Runtorp 3:5, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558097</v>
+        <v>558126</v>
       </c>
       <c r="R29" t="n">
-        <v>6273158</v>
+        <v>6273265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4110,12 +3614,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4124,6 +3628,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4142,55 +3647,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113730308</v>
+        <v>97203469</v>
       </c>
       <c r="B30" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Korsning Bockamossen Ö, Sm</t>
+          <t>Runtorp 3:5, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558096</v>
+        <v>558148</v>
       </c>
       <c r="R30" t="n">
-        <v>6273158</v>
+        <v>6273265</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4217,12 +3724,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4231,6 +3738,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4246,6 +3754,896 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>97203470</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Runtorp 3:5, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>558160</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6273216</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>97203473</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Runtorp 3:5, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>558123</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6273200</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>97203480</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Runtorp 3:5, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>558135</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6273240</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>97203481</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Runtorp 3:5, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>558120</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6273242</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>100195261</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Runtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>557900</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6273172</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>100195381</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Runtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>557863</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6273184</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>100195736</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Runtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>557831</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6273218</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>97203295</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Runtorp 3:5, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>557944</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6273254</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53138-2022 artfynd.xlsx
+++ b/artfynd/A 53138-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203429</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203430</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888542</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89088706</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064018</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064046</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064071</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064089</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,6 +1779,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064100</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888482</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888513</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888622</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888681</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2223,6 +2298,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113730308</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2332,6 +2412,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203468</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2434,6 +2519,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96064086</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2544,6 +2634,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203328</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2654,6 +2749,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203333</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2764,6 +2864,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203359</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2874,6 +2979,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203409</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2984,6 +3094,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203435</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3094,6 +3209,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203438</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3204,6 +3324,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203441</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3314,6 +3439,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203445</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3424,6 +3554,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203451</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3534,6 +3669,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203455</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3644,6 +3784,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203462</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3754,6 +3899,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203469</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3864,6 +4014,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203470</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3974,6 +4129,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203473</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4084,6 +4244,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203480</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4194,6 +4359,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203481</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4304,6 +4474,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100195261</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4414,6 +4589,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100195381</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4528,6 +4708,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100195736</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4644,8 +4829,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203295</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>